--- a/Tennis/postplanner-imports/tfr-postplanner-2026-08-13.xlsx
+++ b/Tennis/postplanner-imports/tfr-postplanner-2026-08-13.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -478,7 +478,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>08/13/2026  13:12</t>
+          <t>08/13/2026  08:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -492,7 +492,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>08/13/2026  14:27</t>
+          <t>08/13/2026  10:30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -508,7 +508,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/13/2026  15:42</t>
+          <t>08/13/2026  12:30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -522,7 +522,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/13/2026  16:57</t>
+          <t>08/13/2026  15:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -537,7 +537,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/13/2026  18:12</t>
+          <t>08/13/2026  17:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -552,7 +552,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/13/2026  19:27</t>
+          <t>08/13/2026  19:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/13/2026  20:42</t>
+          <t>08/13/2026  21:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
